--- a/rules/CORE-000241/negative/01/data/unit-test-coreid-CG0421-negative 1.xlsx
+++ b/rules/CORE-000241/negative/01/data/unit-test-coreid-CG0421-negative 1.xlsx
@@ -1,41 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ce.xpt" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +57,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
-        <bgColor rgb="00FFFFCC"/>
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -58,68 +80,30 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -266,6 +250,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -300,6 +285,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -334,20 +320,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -469,7 +451,46 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -484,12 +505,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
@@ -522,12 +543,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Filename</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
@@ -536,12 +557,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ae.xpt</t>
+          <t>ce.xpt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adverse Events</t>
+          <t>Clinical Events</t>
         </is>
       </c>
     </row>
@@ -556,38 +577,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Error group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Error level</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Row num</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ce.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CEOCCUR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ce.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CEENRF</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ce.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CEOCCUR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ce.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CEENRF</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lorem ipsum dolor sit amet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ce.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CEOCCUR</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ce.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CEENRF</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>123456789</t>
         </is>
       </c>
     </row>
@@ -606,101 +795,101 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>STUDYID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DOMAIN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>AESEQ</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>AETERM</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>AEOCCUR</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>AEENRF</t>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>CESEQ</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>CETERM</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>CEOCCUR</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>CEENRF</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Reported Term for the Adverse Event</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Reported Term for the Clinical Event</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Occurrence Indicator</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>End Relative to Reference Period</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
@@ -710,32 +899,34 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="A4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="F4" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>50</v>
       </c>
     </row>
@@ -747,7 +938,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -758,17 +949,17 @@
       <c r="D5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Uppercase N</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>ONGOING</t>
         </is>
@@ -782,7 +973,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -793,19 +984,19 @@
       <c r="D6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Uppercase N, random text in CEENRF</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>ONGOING</t>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Lorem ipsum dolor sit amet</t>
         </is>
       </c>
     </row>
@@ -817,7 +1008,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -828,15 +1019,18 @@
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Uppercase N, random numerics</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>123456789</v>
       </c>
     </row>
   </sheetData>
